--- a/output_6.xlsx
+++ b/output_6.xlsx
@@ -443,7 +443,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rolling Horizon (re-plan every 12 period(s)) + Safety Stock (SS=35 units for E2801)</t>
+          <t>Rolling Horizon (re-plan every 13 period(s)) + Safety Stock (SS=42 units for E2801)</t>
         </is>
       </c>
     </row>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Within each window, future demand is still uncertain. SS=35 units (≈95% CSL, based on sigma_error=24.9) buffers small within-window surprises without incurring backorders.</t>
+          <t>Within each window, future demand is still uncertain. SS=42 units (≈95% CSL, based on sigma_error=24.9) buffers small within-window surprises without incurring backorders.</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>547941.8</t>
+          <t>540417.8</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5744.8</t>
+          <t>13268.8</t>
         </is>
       </c>
     </row>
@@ -575,7 +575,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>98.16%</t>
+          <t>98.79%</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>364411.8</v>
+        <v>366387.8</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27750</v>
+        <v>18250</v>
       </c>
     </row>
     <row r="9">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>547941.8</v>
+        <v>540417.8</v>
       </c>
     </row>
     <row r="10">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9816</v>
+        <v>0.9879</v>
       </c>
     </row>
     <row r="16">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -849,10 +849,10 @@
         <v>30000</v>
       </c>
       <c r="D2" t="n">
-        <v>40326</v>
+        <v>41182</v>
       </c>
       <c r="E2" t="n">
-        <v>70326</v>
+        <v>71182</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -874,10 +874,10 @@
         <v>17500</v>
       </c>
       <c r="D3" t="n">
-        <v>20209</v>
+        <v>20469.4</v>
       </c>
       <c r="E3" t="n">
-        <v>37709</v>
+        <v>37969.4</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -949,10 +949,10 @@
         <v>10000</v>
       </c>
       <c r="D6" t="n">
-        <v>72564.8</v>
+        <v>73172.39999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>82564.8</v>
+        <v>83172.39999999999</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -999,10 +999,10 @@
         <v>22500</v>
       </c>
       <c r="D8" t="n">
-        <v>146112</v>
+        <v>146364</v>
       </c>
       <c r="E8" t="n">
-        <v>168612</v>
+        <v>168864</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         <v>132000</v>
       </c>
       <c r="D9" t="n">
-        <v>364411.8</v>
+        <v>366387.8</v>
       </c>
       <c r="E9" t="n">
-        <v>496411.8</v>
+        <v>498387.8</v>
       </c>
       <c r="F9" t="n">
         <v>600</v>
@@ -1042,10 +1042,10 @@
         <v>21180</v>
       </c>
       <c r="J9" t="n">
-        <v>27750</v>
+        <v>18250</v>
       </c>
       <c r="K9" t="n">
-        <v>547941.8</v>
+        <v>540417.8</v>
       </c>
     </row>
   </sheetData>
@@ -1259,7 +1259,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>-0</v>
@@ -1268,7 +1268,7 @@
         <v>-0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>-0</v>
@@ -1279,7 +1279,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>-0</v>
@@ -1288,7 +1288,7 @@
         <v>-0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>-0</v>
@@ -1339,19 +1339,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="15">
@@ -1362,16 +1362,16 @@
         <v>-0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E15" t="n">
         <v>-0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="16">
@@ -1382,16 +1382,16 @@
         <v>-0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E16" t="n">
         <v>-0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="17">
@@ -1422,16 +1422,16 @@
         <v>-0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E18" t="n">
         <v>-0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="19">
@@ -1442,16 +1442,16 @@
         <v>-0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E19" t="n">
         <v>-0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="20">
@@ -1519,19 +1519,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="24">
@@ -1539,7 +1539,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
         <v>-0</v>
@@ -1548,7 +1548,7 @@
         <v>-0</v>
       </c>
       <c r="E24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>-0</v>
@@ -1559,19 +1559,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="26">
@@ -1582,16 +1582,16 @@
         <v>-0</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E26" t="n">
         <v>-0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="27">
@@ -1602,16 +1602,16 @@
         <v>-0</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E27" t="n">
         <v>-0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="28">
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2176</v>
+        <v>2288</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1908,10 +1908,10 @@
         <v>3804</v>
       </c>
       <c r="N2" t="n">
-        <v>2092</v>
+        <v>3804</v>
       </c>
       <c r="O2" t="n">
-        <v>3804</v>
+        <v>2588</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -1975,7 +1975,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2432</v>
+        <v>2516</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -2011,7 +2011,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4422</v>
+        <v>4794</v>
       </c>
       <c r="Q3" t="n">
         <v>5706</v>
@@ -2099,7 +2099,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5922</v>
+        <v>5964</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -2117,7 +2117,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>5064</v>
+        <v>5250</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -2184,7 +2184,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>20727</v>
+        <v>20874</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>17724</v>
+        <v>18375</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -2272,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2144</v>
+        <v>2172</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -2311,7 +2311,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3376</v>
+        <v>3500</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -2393,7 +2393,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2961</v>
+        <v>2982</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -2411,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2532</v>
+        <v>2625</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -2496,7 +2496,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>987</v>
+        <v>994</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2514,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>844</v>
+        <v>875</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -2964,7 +2964,7 @@
         <v>7608</v>
       </c>
       <c r="R2" t="n">
-        <v>9700</v>
+        <v>11412</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -3061,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>4422</v>
+        <v>4794</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -3325,25 +3325,25 @@
         <v>3200</v>
       </c>
       <c r="I6" t="n">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="J6" t="n">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="K6" t="n">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="L6" t="n">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="M6" t="n">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="N6" t="n">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="O6" t="n">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -3543,49 +3543,49 @@
         <v>432</v>
       </c>
       <c r="Q8" t="n">
-        <v>1233</v>
+        <v>1240</v>
       </c>
       <c r="R8" t="n">
-        <v>1040</v>
+        <v>1047</v>
       </c>
       <c r="S8" t="n">
-        <v>839</v>
+        <v>846</v>
       </c>
       <c r="T8" t="n">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="U8" t="n">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="V8" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="W8" t="n">
-        <v>756</v>
+        <v>794</v>
       </c>
       <c r="X8" t="n">
-        <v>509</v>
+        <v>547</v>
       </c>
       <c r="Y8" t="n">
-        <v>276</v>
+        <v>314</v>
       </c>
       <c r="Z8" t="n">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>636</v>
+        <v>598</v>
       </c>
       <c r="AC8" t="n">
-        <v>465</v>
+        <v>427</v>
       </c>
       <c r="AD8" t="n">
-        <v>268</v>
+        <v>230</v>
       </c>
       <c r="AE8" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4691,7 +4691,7 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>

--- a/output_6.xlsx
+++ b/output_6.xlsx
@@ -7,14 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Method Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Cost per Part" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Overtime" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Production Plan" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Inventory Plan" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Setup Decisions" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Backorders" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Cost per Part" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Overtime" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Production Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Inventory Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Setup Decisions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Backorders" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -420,163 +419,179 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Metric</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Rolling Horizon (re-plan every 13 period(s)) + Safety Stock (SS=42 units for E2801)</t>
-        </is>
+          <t>Setup Cost (EUR)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>132000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Why Rolling Horizon</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Re-optimizing regularly absorbs forecast errors by updating plans with actual inventory levels, preventing the demand drift that caused backorders in week 26 &amp; 30 in 5b.</t>
-        </is>
+          <t>Holding Cost (EUR)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>366387.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Why Safety Stock</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Within each window, future demand is still uncertain. SS=42 units (≈95% CSL, based on sigma_error=24.9) buffers small within-window surprises without incurring backorders.</t>
-        </is>
+          <t>Overtime Cost X (EUR)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Modernization</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Fixed from 5a: WS-X +200 units, WS-Y +14.1200%. One-time cost EUR 23,180.00.</t>
-        </is>
+          <t>Overtime Cost Y (EUR)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Overtime</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Re-optimized every window, so overtime is only used when truly needed given actual inventory state.</t>
-        </is>
+          <t>Modernization Cost X (EUR)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5b Total Cost (EUR)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>553686.6</t>
-        </is>
+          <t>Modernization Cost Y (EUR)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>21180</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6  Total Cost (EUR)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>540417.8</t>
-        </is>
+          <t>Backorder Cost (EUR)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>18250</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cost improvement (EUR)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>13268.8</t>
-        </is>
+          <t>Total Cost (EUR)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>540417.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5b Service Level</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>93.33%</t>
-        </is>
+          <t>Added capacity WS-X (units)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6  Service Level</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>96.67%</t>
-        </is>
+          <t>Added capacity WS-Y (%)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>14.12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5b Fill Rate</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>97.52%</t>
-        </is>
+          <t>New capacity WS-X (units)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6  Fill Rate</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>98.79%</t>
-        </is>
+          <t>New capacity WS-Y (min)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>11412</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Service Level</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.9667</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Fill Rate</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.9879</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Rolling Horizon Frequency</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Safety Stock E2801 (units)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -590,179 +605,276 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Part</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Num Setups</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Setup Cost (EUR)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Holding Cost (EUR)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Total Cost (EUR)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Overtime Cost X (EUR)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Overtime Cost Y (EUR)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Modernization Cost X (EUR)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Modernization Cost Y (EUR)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Backorder Cost (EUR)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Grand Total (EUR)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Setup Cost (EUR)</t>
+          <t>B1401</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>132000</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>41182</v>
+      </c>
+      <c r="E2" t="n">
+        <v>71182</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Holding Cost (EUR)</t>
+          <t>B2302</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>366387.8</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="C3" t="n">
+        <v>17500</v>
+      </c>
+      <c r="D3" t="n">
+        <v>20469.4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>37969.4</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Overtime Cost X (EUR)</t>
+          <t>B3201</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>600</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>26000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>46800</v>
+      </c>
+      <c r="E4" t="n">
+        <v>72800</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Overtime Cost Y (EUR)</t>
+          <t>B4702</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>38400</v>
+      </c>
+      <c r="E5" t="n">
+        <v>48400</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Modernization Cost X (EUR)</t>
+          <t>V1501</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2000</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>73172.39999999999</v>
+      </c>
+      <c r="E6" t="n">
+        <v>83172.39999999999</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Modernization Cost Y (EUR)</t>
+          <t>V6302</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21180</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>16000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>16000</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Backorder Cost (EUR)</t>
+          <t>E2801</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18250</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>22500</v>
+      </c>
+      <c r="D8" t="n">
+        <v>146364</v>
+      </c>
+      <c r="E8" t="n">
+        <v>168864</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Total Cost (EUR)</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>40</v>
+      </c>
+      <c r="C9" t="n">
+        <v>132000</v>
+      </c>
+      <c r="D9" t="n">
+        <v>366387.8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>498387.8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>600</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I9" t="n">
+        <v>21180</v>
+      </c>
+      <c r="J9" t="n">
+        <v>18250</v>
+      </c>
+      <c r="K9" t="n">
         <v>540417.8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Added capacity WS-X (units)</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Added capacity WS-Y (%)</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>14.12</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>New capacity WS-X (units)</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>New capacity WS-Y (min)</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>11412</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Service Level</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.9667</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Fill Rate</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0.9879</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Rolling Horizon Frequency</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Safety Stock E2801 (units)</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -776,276 +888,639 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Part</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Num Setups</t>
+          <t>OT Units X</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Setup Cost (EUR)</t>
+          <t>OT Minutes Y</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Holding Cost (EUR)</t>
+          <t>OT Hours Y</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Total Cost (EUR)</t>
+          <t>OT Cost X (EUR)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Overtime Cost X (EUR)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Overtime Cost Y (EUR)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Modernization Cost X (EUR)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Modernization Cost Y (EUR)</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Backorder Cost (EUR)</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Grand Total (EUR)</t>
+          <t>OT Cost Y (EUR)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>B1401</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>300</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>600</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="C2" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>41182</v>
-      </c>
-      <c r="E2" t="n">
-        <v>71182</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>B2302</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C3" t="n">
-        <v>17500</v>
-      </c>
-      <c r="D3" t="n">
-        <v>20469.4</v>
-      </c>
-      <c r="E3" t="n">
-        <v>37969.4</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>B3201</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C4" t="n">
-        <v>26000</v>
-      </c>
-      <c r="D4" t="n">
-        <v>46800</v>
-      </c>
-      <c r="E4" t="n">
-        <v>72800</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>B4702</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>38400</v>
-      </c>
-      <c r="E5" t="n">
-        <v>48400</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>V1501</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D6" t="n">
-        <v>73172.39999999999</v>
-      </c>
-      <c r="E6" t="n">
-        <v>83172.39999999999</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>V6302</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C7" t="n">
-        <v>16000</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>16000</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>E2801</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C8" t="n">
-        <v>22500</v>
-      </c>
-      <c r="D8" t="n">
-        <v>146364</v>
-      </c>
-      <c r="E8" t="n">
-        <v>168864</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>40</v>
-      </c>
-      <c r="C9" t="n">
-        <v>132000</v>
-      </c>
-      <c r="D9" t="n">
-        <v>366387.8</v>
-      </c>
-      <c r="E9" t="n">
-        <v>498387.8</v>
-      </c>
-      <c r="F9" t="n">
-        <v>600</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I9" t="n">
-        <v>21180</v>
-      </c>
-      <c r="J9" t="n">
-        <v>18250</v>
-      </c>
-      <c r="K9" t="n">
-        <v>540417.8</v>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1059,639 +1534,1037 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:AE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Period</t>
+          <t>Part</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>OT Units X</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>OT Minutes Y</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>OT Hours Y</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>OT Cost X (EUR)</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>OT Cost Y (EUR)</t>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>W19</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>W20</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>W21</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>W22</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>W23</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>W24</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>W25</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>W26</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>W27</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>W28</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>W29</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>W30</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>B1401</t>
+        </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>2288</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>3804</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3804</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3804</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3804</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3804</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3804</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3804</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2588</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>3656</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3804</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3804</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B2302</t>
+        </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>2516</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5706</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5706</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4794</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5706</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2742</v>
+      </c>
+      <c r="V3" t="n">
+        <v>5706</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>B3201</t>
+        </is>
       </c>
       <c r="B4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>2600</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>5964</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5250</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>4224</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>B4702</t>
+        </is>
       </c>
       <c r="B5" t="n">
-        <v>-0</v>
+        <v>24100</v>
       </c>
       <c r="C5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-0</v>
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>20874</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>18375</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>14784</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>V1501</t>
+        </is>
       </c>
       <c r="B6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>-0</v>
+        <v>2172</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3804</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3500</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2816</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>V6302</t>
+        </is>
       </c>
       <c r="B7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>-0</v>
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3900</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2982</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2625</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2112</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>E2801</t>
+        </is>
       </c>
       <c r="B8" t="n">
-        <v>-0</v>
+        <v>650</v>
       </c>
       <c r="C8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-0</v>
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1300</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>994</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>875</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>704</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Forecast Demand E2801</t>
+        </is>
       </c>
       <c r="B9" t="n">
-        <v>300</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>-0</v>
+        <v>144</v>
       </c>
       <c r="D9" t="n">
-        <v>-0</v>
+        <v>263</v>
       </c>
       <c r="E9" t="n">
-        <v>600</v>
+        <v>123</v>
       </c>
       <c r="F9" t="n">
-        <v>-0</v>
+        <v>171</v>
+      </c>
+      <c r="G9" t="n">
+        <v>195</v>
+      </c>
+      <c r="H9" t="n">
+        <v>414</v>
+      </c>
+      <c r="I9" t="n">
+        <v>147</v>
+      </c>
+      <c r="J9" t="n">
+        <v>129</v>
+      </c>
+      <c r="K9" t="n">
+        <v>245</v>
+      </c>
+      <c r="L9" t="n">
+        <v>208</v>
+      </c>
+      <c r="M9" t="n">
+        <v>178</v>
+      </c>
+      <c r="N9" t="n">
+        <v>168</v>
+      </c>
+      <c r="O9" t="n">
+        <v>208</v>
+      </c>
+      <c r="P9" t="n">
+        <v>173</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>168</v>
+      </c>
+      <c r="R9" t="n">
+        <v>181</v>
+      </c>
+      <c r="S9" t="n">
+        <v>188</v>
+      </c>
+      <c r="T9" t="n">
+        <v>212</v>
+      </c>
+      <c r="U9" t="n">
+        <v>253</v>
+      </c>
+      <c r="V9" t="n">
+        <v>219</v>
+      </c>
+      <c r="W9" t="n">
+        <v>196</v>
+      </c>
+      <c r="X9" t="n">
+        <v>226</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>239</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>220</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>199</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>183</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>149</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>167</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>205</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Realized Demand E2801</t>
+        </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C10" t="n">
-        <v>-0</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
-        <v>-0</v>
+        <v>213</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="F10" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="n">
-        <v>-0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="n">
-        <v>-0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="n">
-        <v>-0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="n">
-        <v>-0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="n">
-        <v>-0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D25" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="n">
-        <v>-0</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="n">
-        <v>-0</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D27" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="n">
-        <v>-0</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="n">
-        <v>-0</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="n">
-        <v>-0</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="n">
-        <v>-0</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
+        <v>148</v>
+      </c>
+      <c r="G10" t="n">
+        <v>162</v>
+      </c>
+      <c r="H10" t="n">
+        <v>367</v>
+      </c>
+      <c r="I10" t="n">
+        <v>129</v>
+      </c>
+      <c r="J10" t="n">
+        <v>110</v>
+      </c>
+      <c r="K10" t="n">
+        <v>286</v>
+      </c>
+      <c r="L10" t="n">
+        <v>241</v>
+      </c>
+      <c r="M10" t="n">
+        <v>212</v>
+      </c>
+      <c r="N10" t="n">
+        <v>199</v>
+      </c>
+      <c r="O10" t="n">
+        <v>236</v>
+      </c>
+      <c r="P10" t="n">
+        <v>187</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>186</v>
+      </c>
+      <c r="R10" t="n">
+        <v>193</v>
+      </c>
+      <c r="S10" t="n">
+        <v>201</v>
+      </c>
+      <c r="T10" t="n">
+        <v>228</v>
+      </c>
+      <c r="U10" t="n">
+        <v>237</v>
+      </c>
+      <c r="V10" t="n">
+        <v>253</v>
+      </c>
+      <c r="W10" t="n">
+        <v>209</v>
+      </c>
+      <c r="X10" t="n">
+        <v>247</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>233</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>195</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>192</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>179</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>171</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>197</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -1705,7 +2578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE10"/>
+  <dimension ref="A1:AE8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1872,70 +2745,70 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2288</v>
+        <v>6400</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
         <v>3804</v>
       </c>
-      <c r="G2" t="n">
+      <c r="K2" t="n">
+        <v>7608</v>
+      </c>
+      <c r="L2" t="n">
+        <v>11412</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>3804</v>
       </c>
-      <c r="H2" t="n">
-        <v>3804</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3804</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>3804</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3804</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3804</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2588</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>7608</v>
       </c>
       <c r="R2" t="n">
+        <v>11412</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
         <v>3656</v>
       </c>
-      <c r="S2" t="n">
-        <v>3804</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3804</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>7460</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -1969,16 +2842,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="D3" t="n">
-        <v>2516</v>
+        <v>4000</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1993,14 +2866,14 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>5706</v>
       </c>
-      <c r="K3" t="n">
-        <v>5706</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
@@ -2011,14 +2884,14 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
         <v>4794</v>
       </c>
-      <c r="Q3" t="n">
-        <v>5706</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
@@ -2026,13 +2899,13 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
         <v>2742</v>
-      </c>
-      <c r="V3" t="n">
-        <v>5706</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -2066,19 +2939,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="F4" t="n">
-        <v>2600</v>
+        <v>5200</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -2099,7 +2972,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5964</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -2117,7 +2990,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>5250</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -2132,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>4224</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -2163,19 +3036,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24100</v>
+        <v>3200</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -2184,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>20874</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -2202,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>18375</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -2217,7 +3090,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>14784</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2260,46 +3133,46 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="F6" t="n">
-        <v>2172</v>
+        <v>3200</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="M6" t="n">
-        <v>3804</v>
+        <v>172</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -2311,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -2326,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2816</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -2372,7 +3245,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>3900</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -2393,7 +3266,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2982</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -2411,7 +3284,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2625</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -2426,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2112</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -2454,288 +3327,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>650</v>
+        <v>1230</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1728</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1515</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1409</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1261</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1099</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>732</v>
       </c>
       <c r="I8" t="n">
-        <v>1300</v>
+        <v>603</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1793</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1507</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1266</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1054</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>855</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>619</v>
       </c>
       <c r="P8" t="n">
-        <v>994</v>
+        <v>432</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1240</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1047</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>846</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>618</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="V8" t="n">
-        <v>875</v>
+        <v>128</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>794</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>547</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>314</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="AA8" t="n">
-        <v>704</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>598</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>427</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Forecast Demand E2801</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>136</v>
-      </c>
-      <c r="C9" t="n">
-        <v>144</v>
-      </c>
-      <c r="D9" t="n">
-        <v>263</v>
-      </c>
-      <c r="E9" t="n">
-        <v>123</v>
-      </c>
-      <c r="F9" t="n">
-        <v>171</v>
-      </c>
-      <c r="G9" t="n">
-        <v>195</v>
-      </c>
-      <c r="H9" t="n">
-        <v>414</v>
-      </c>
-      <c r="I9" t="n">
-        <v>147</v>
-      </c>
-      <c r="J9" t="n">
-        <v>129</v>
-      </c>
-      <c r="K9" t="n">
-        <v>245</v>
-      </c>
-      <c r="L9" t="n">
-        <v>208</v>
-      </c>
-      <c r="M9" t="n">
-        <v>178</v>
-      </c>
-      <c r="N9" t="n">
-        <v>168</v>
-      </c>
-      <c r="O9" t="n">
-        <v>208</v>
-      </c>
-      <c r="P9" t="n">
-        <v>173</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>168</v>
-      </c>
-      <c r="R9" t="n">
-        <v>181</v>
-      </c>
-      <c r="S9" t="n">
-        <v>188</v>
-      </c>
-      <c r="T9" t="n">
-        <v>212</v>
-      </c>
-      <c r="U9" t="n">
-        <v>253</v>
-      </c>
-      <c r="V9" t="n">
-        <v>219</v>
-      </c>
-      <c r="W9" t="n">
-        <v>196</v>
-      </c>
-      <c r="X9" t="n">
-        <v>226</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>239</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>220</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>199</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>183</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>149</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>167</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Realized Demand E2801</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>120</v>
-      </c>
-      <c r="C10" t="n">
-        <v>152</v>
-      </c>
-      <c r="D10" t="n">
-        <v>213</v>
-      </c>
-      <c r="E10" t="n">
-        <v>106</v>
-      </c>
-      <c r="F10" t="n">
-        <v>148</v>
-      </c>
-      <c r="G10" t="n">
-        <v>162</v>
-      </c>
-      <c r="H10" t="n">
-        <v>367</v>
-      </c>
-      <c r="I10" t="n">
-        <v>129</v>
-      </c>
-      <c r="J10" t="n">
-        <v>110</v>
-      </c>
-      <c r="K10" t="n">
-        <v>286</v>
-      </c>
-      <c r="L10" t="n">
-        <v>241</v>
-      </c>
-      <c r="M10" t="n">
-        <v>212</v>
-      </c>
-      <c r="N10" t="n">
-        <v>199</v>
-      </c>
-      <c r="O10" t="n">
-        <v>236</v>
-      </c>
-      <c r="P10" t="n">
-        <v>187</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>186</v>
-      </c>
-      <c r="R10" t="n">
-        <v>193</v>
-      </c>
-      <c r="S10" t="n">
-        <v>201</v>
-      </c>
-      <c r="T10" t="n">
-        <v>228</v>
-      </c>
-      <c r="U10" t="n">
-        <v>237</v>
-      </c>
-      <c r="V10" t="n">
-        <v>253</v>
-      </c>
-      <c r="W10" t="n">
-        <v>209</v>
-      </c>
-      <c r="X10" t="n">
-        <v>247</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>233</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>195</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>192</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>179</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>171</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>197</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>228</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2916,70 +3595,70 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6400</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6400</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>6400</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>6400</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>3804</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>7608</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>11412</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>3804</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>7608</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>11412</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>3656</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>7460</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -3013,16 +3692,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4000</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -3037,13 +3716,13 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>5706</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -3055,13 +3734,13 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>4794</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -3070,13 +3749,13 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>2742</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -3110,19 +3789,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>5200</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -3143,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -3161,7 +3840,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -3176,7 +3855,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -3207,19 +3886,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3200</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -3228,7 +3907,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -3246,7 +3925,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -3261,7 +3940,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -3304,46 +3983,46 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3200</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>172</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -3355,7 +4034,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -3370,7 +4049,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -3416,7 +4095,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -3437,7 +4116,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3455,7 +4134,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3470,7 +4149,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -3498,94 +4177,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1230</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>1728</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1515</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1409</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1261</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1099</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>732</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>603</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>1793</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1507</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1266</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1054</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>855</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>619</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>432</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1240</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1047</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>846</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>618</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>381</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>128</v>
+        <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>794</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>547</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>314</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB8" t="n">
-        <v>598</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>427</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3599,856 +4278,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Part</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>W10</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>W11</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>W12</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>W13</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>W14</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>W15</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>W16</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>W17</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>W18</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>W19</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>W20</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>W21</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>W22</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>W23</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>W24</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>W25</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>W26</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>W27</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>W28</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>W29</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>W30</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>B1401</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>B2302</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>B3201</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>B4702</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>V1501</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>V6302</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>E2801</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:AE2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
